--- a/fuction_ensemble/redes-ensemble-s/Teste04/results.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:FK17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,90 +446,820 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_7</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_8</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_9</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_6</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_10</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_5</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_4</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_3</t>
+          <t>model_23_9_12</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_2</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>model_22_9_1</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>model_22_8_8</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>model_22_8_7</t>
+          <t>model_23_9_3</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>model_22_8_6</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>model_22_8_5</t>
+          <t>model_23_9_16</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>model_22_8_4</t>
+          <t>model_23_9_17</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>model_22_8_3</t>
+          <t>model_23_9_18</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>model_23_9_19</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_9_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_9_20</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_9_21</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_9_22</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_9_23</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_9_24</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_9_1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_9_0</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_8_1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_8_2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_8_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_8_4</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_0</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_1</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_3</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_4</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_5</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_6</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_8</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_7</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_9</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_12</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_19</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_14</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_15</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_16</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_17</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_18</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_22</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_23</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_24</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_20</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_21</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_8_0</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_7_13</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_0</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_1</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_4</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_3</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_5</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_6</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_7</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_9</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_23</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_13</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_14</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_16</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_17</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_18</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_24</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_22</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_21</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_15</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_20</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_19</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_12</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_11</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_10</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>model_23_6_8</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_21</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_20</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_22</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_19</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_23</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_24</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_18</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_17</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_16</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_15</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_14</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_13</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_12</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_11</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_10</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_9</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_8</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_7</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_6</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_8_0</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_5</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_8_1</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_8_2</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_4</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_8_3</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_8_4</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_3</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_2</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>model_19_9_4</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_1</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>model_19_9_3</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_21</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_9</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_24</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_24</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_11</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_1</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_2</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_3</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_4</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_5</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_6</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_7</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_8</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_10</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_12</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_23</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_13</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_14</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_15</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_16</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_17</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_18</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_19</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_20</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_21</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_22</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_7_0</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_10</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_23</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_11</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_1</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_2</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_3</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_4</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_5</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_6</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_7</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_8</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_9</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_12</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_13</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_17</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_0</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_22</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_19</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_18</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_20</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_16</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_15</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>model_25_9_14</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>model_21_9_0</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
           <t>media</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>desvio padrao</t>
         </is>
@@ -546,58 +1276,496 @@
         <v>0.04683538599288443</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7854564189910889</v>
+        <v>-0.4789111018180847</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7944192886352539</v>
+        <v>-0.4762213230133057</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8024849891662598</v>
+        <v>-0.4819046258926392</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7754950523376465</v>
+        <v>-0.4738030433654785</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8097434043884277</v>
+        <v>-0.4716293811798096</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7644279003143311</v>
+        <v>-0.4852378368377686</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7521268129348755</v>
+        <v>-0.4696770310401917</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7384583950042725</v>
+        <v>-0.4679208993911743</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7232685089111328</v>
+        <v>-0.488946795463562</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7063889503479004</v>
+        <v>-0.4663411974906921</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.667715311050415</v>
+        <v>-0.4649219512939453</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6674599647521973</v>
+        <v>-0.4930802583694458</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6670697927474976</v>
+        <v>-0.4636445045471191</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.666502833366394</v>
+        <v>-0.4624958634376526</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.6657059192657471</v>
+        <v>-0.4614629149436951</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6646140813827515</v>
+        <v>-0.4605345726013184</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6826177786825474</v>
+        <v>-0.4596981406211853</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1956968460543754</v>
+        <v>-0.4976828098297119</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.4589465856552124</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.4582710862159729</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.4576613903045654</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.4571139812469482</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.4566209316253662</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.5028126239776611</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.5085307359695435</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.5416316986083984</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.5423901081085205</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.5430779457092285</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.5437009334564209</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.5299005508422852</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.5299015045166016</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.5299015045166016</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.5299012660980225</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.5299022197723389</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.5299018621444702</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.5299021005630493</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.5299019813537598</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.5299023389816284</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.5299018621444702</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.5299015045166016</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.5299021005630493</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-0.5299022197723389</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.5299011468887329</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-0.5177657604217529</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-0.5177608728408813</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-0.5177431106567383</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-0.5177357196807861</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-0.5177364349365234</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-0.5177347660064697</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-0.5177336931228638</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.5177305936813354</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-0.5177308320999146</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>-0.5177303552627563</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>-0.5177308320999146</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>-0.5177308320999146</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>-0.5177308320999146</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>-0.5177305936813354</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>-0.2222141176462173</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>-0.2206815630197525</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>-0.2235675007104874</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>-0.218941405415535</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-0.2247611433267593</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>-0.2258167415857315</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-0.216962531208992</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>-0.2147072106599808</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>-0.2121333628892899</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>-0.2091940194368362</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>-0.2058275490999222</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>-0.2019659429788589</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>-0.1975295692682266</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-0.1924273520708084</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>-0.1865491420030594</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>-0.1797702461481094</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>-0.1719450503587723</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>-0.1629051715135574</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>-0.1524601727724075</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>0.2007284909486771</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.1403957158327103</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0.1796724647283554</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.1600431352853775</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.1264640837907791</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.1418528109788895</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.12507463991642</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.110398069024086</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.09190090000629425</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.3671675324440002</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.07065536081790924</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.2750052809715271</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>-0.9976723194122314</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>-0.04632432386279106</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>-0.5816794443899335</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>0.3200066581304668</v>
       </c>
     </row>
     <row r="3">
@@ -611,58 +1779,496 @@
         <v>-1.816919697522331</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.945871114730835</v>
+        <v>-1.206557989120483</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.945011377334595</v>
+        <v>-1.205464124679565</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.944231271743774</v>
+        <v>-1.207794189453125</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.946824789047241</v>
+        <v>-1.204495191574097</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.943528890609741</v>
+        <v>-1.20363450050354</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.947880029678345</v>
+        <v>-1.20919406414032</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.949045896530151</v>
+        <v>-1.202870965003967</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.950332403182983</v>
+        <v>-1.202191591262817</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.951751470565796</v>
+        <v>-1.210779428482056</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.953316926956177</v>
+        <v>-1.201586008071899</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.899572610855103</v>
+        <v>-1.201046228408813</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.891547918319702</v>
+        <v>-1.21258282661438</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.882574796676636</v>
+        <v>-1.20056414604187</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.872534990310669</v>
+        <v>-1.200134873390198</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.861291170120239</v>
+        <v>-1.199751138687134</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.848687410354614</v>
+        <v>-1.199406147003174</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.797113103796408</v>
+        <v>-1.199099659919739</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5115817096296968</v>
+        <v>-1.214635014533997</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-1.198824286460876</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1.198578357696533</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-1.198356032371521</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1.198159337043762</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1.197980761528015</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1.21697735786438</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.219658970832825</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-1.248878240585327</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1.247948408126831</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-1.247114300727844</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-1.246368885040283</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-1.265121936798096</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1.265121102333069</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-1.265120387077332</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-1.265120625495911</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-1.265118718147278</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-1.265118598937988</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-1.265117406845093</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-1.265115976333618</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-1.265116930007935</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1.265115857124329</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-1.26511549949646</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1.26511538028717</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-1.26511549949646</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-1.265115141868591</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-1.26511538028717</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-1.359560370445251</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-1.359562754631042</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-1.35957145690918</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-1.359575033187866</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-1.35957407951355</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-1.359575271606445</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-1.359575986862183</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>-1.359578132629395</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>-1.042005181312561</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>-1.046356439590454</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>-1.038075923919678</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>-1.05117654800415</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>-1.034529685974121</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>-1.031330823898315</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>-1.056514739990234</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>-1.062421798706055</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>-1.06895899772644</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>-1.0761878490448</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>-1.084181070327759</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>-1.093016743659973</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>-1.102779269218445</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>-1.113559603691101</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>-1.125463247299194</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>-1.13860023021698</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>-1.153092622756958</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>-1.169078707695007</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>-1.186704039573669</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>-1.142447829246521</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>-1.206135988235474</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>-1.163071513175964</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>-1.182774066925049</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>-1.227558970451355</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>-1.201359152793884</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>-1.218721866607666</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>-1.251174926757812</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>-1.277212381362915</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>-5.951960563659668</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>-1.305925726890564</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>-5.909016132354736</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EF3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EH3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EI3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EQ3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="ER3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="ES3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="ET3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EU3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EW3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EX3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EY3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="EZ3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FA3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FB3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FC3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FD3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FE3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FF3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FG3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FH3" t="n">
+        <v>-4.340785980224609</v>
+      </c>
+      <c r="FI3" t="n">
+        <v>-1.337601900100708</v>
+      </c>
+      <c r="FJ3" t="n">
+        <v>-2.25084833507157</v>
+      </c>
+      <c r="FK3" t="n">
+        <v>1.489566228745888</v>
       </c>
     </row>
     <row r="4">
@@ -676,58 +2282,496 @@
         <v>-3.660577247945794</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.915147066116333</v>
+        <v>-3.576294660568237</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.922759771347046</v>
+        <v>-3.582678556442261</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.92962384223938</v>
+        <v>-3.569199800491333</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.906708478927612</v>
+        <v>-3.588419198989868</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.935811758041382</v>
+        <v>-3.593584775924683</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.897355794906616</v>
+        <v>-3.561314344406128</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.886996984481812</v>
+        <v>-3.598230600357056</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.875530958175659</v>
+        <v>-3.602410554885864</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.862846612930298</v>
+        <v>-3.552548170089722</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.848828077316284</v>
+        <v>-3.606171369552612</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.804781198501587</v>
+        <v>-3.609553575515747</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.803264379501343</v>
+        <v>-3.542803525924683</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.801591634750366</v>
+        <v>-3.612595796585083</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.799753904342651</v>
+        <v>-3.615334272384644</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.79773211479187</v>
+        <v>-3.617798566818237</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.795518159866333</v>
+        <v>-3.620013475418091</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.849695763775433</v>
+        <v>-3.622009992599487</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07139843462234867</v>
+        <v>-3.531973600387573</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-3.623804330825806</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-3.625418424606323</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-3.626872301101685</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-3.628180265426636</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-3.629355669021606</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-3.519940137863159</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-3.506572008132935</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-3.37062668800354</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-3.375391960144043</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-3.379684925079346</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-3.383554697036743</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-3.301324605941772</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-3.301320314407349</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-3.301316499710083</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-3.301313400268555</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-3.301310539245605</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-3.301307678222656</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-3.301303863525391</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-3.301298856735229</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-3.301301002502441</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-3.301296710968018</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-3.301294326782227</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-3.301293134689331</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-3.301291465759277</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-3.301287412643433</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-3.301287889480591</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-3.739770650863647</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-3.739771604537964</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-3.739769697189331</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-3.739771127700806</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-3.739771127700806</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-3.739771127700806</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-3.739770174026489</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-3.739771127700806</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>-3.368101835250854</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-3.368841171264648</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-3.367434501647949</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-3.369660377502441</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-3.366831302642822</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>-3.366288661956787</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-3.370569705963135</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-3.371577024459839</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-3.372690200805664</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-3.373922824859619</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-3.375287532806396</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-3.376797199249268</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-3.378466129302979</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>-3.380312919616699</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-3.382355213165283</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-3.384611845016479</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-3.38710880279541</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-3.389869213104248</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-3.392922878265381</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>-3.367203235626221</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-3.39630651473999</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>-3.374311447143555</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>-3.38066554069519</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-3.400058031082153</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>-3.386310815811157</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-3.391306400299072</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-3.404226303100586</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>-3.40886926651001</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-3.806654691696167</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-3.41405725479126</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>-3.785362958908081</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>-2.668647527694702</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>-3.419878005981445</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>-3.244000727111384</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.4101715320858336</v>
       </c>
     </row>
     <row r="5">
@@ -741,58 +2785,496 @@
         <v>-0.06163979365409215</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1676051765680313</v>
+        <v>0.1591642051935196</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1670486181974411</v>
+        <v>0.1600006371736526</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1665562838315964</v>
+        <v>0.1582365483045578</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1682325452566147</v>
+        <v>0.1607555001974106</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1661193817853928</v>
+        <v>0.1614352613687515</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1689433306455612</v>
+        <v>0.1572101265192032</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1697476655244827</v>
+        <v>0.1620476096868515</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1706605106592178</v>
+        <v>0.1626006513834</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1716951280832291</v>
+        <v>0.1560716181993484</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1728725880384445</v>
+        <v>0.1630998104810715</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1832071989774704</v>
+        <v>0.1635490506887436</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1842245906591415</v>
+        <v>0.1548129469156265</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1853517442941666</v>
+        <v>0.1639539450407028</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1866027265787125</v>
+        <v>0.1643170863389969</v>
       </c>
       <c r="R5" t="n">
-        <v>0.187992200255394</v>
+        <v>0.1646454483270645</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1895323246717453</v>
+        <v>0.1649416536092758</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1614560129630911</v>
+        <v>0.1652082353830338</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05813054023552236</v>
+        <v>0.1534189730882645</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1654475480318069</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1656647771596909</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1658577173948288</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.1660337895154953</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.1661904603242874</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1518784910440445</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.150173619389534</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1283098608255386</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.1294970959424973</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1305543035268784</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.1314945071935654</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.1054754704236984</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1054758280515671</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1054748743772507</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1054753512144089</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1054758280515671</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1054768115282059</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.1054772883653641</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.1054779142141342</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.1054775565862656</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.1054783910512924</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.1054781526327133</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.1054786592721939</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.105478510260582</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.06986801326274872</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.06986801326274872</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.06987009942531586</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.06987093389034271</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.06987093389034271</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.06987093389034271</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.06987093389034271</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.0698724240064621</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.0698724240064621</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.06987254321575165</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.0698724240064621</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.0698724240064621</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.0698724240064621</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.0698724240064621</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.3508887588977814</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.3501452505588531</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.3515569269657135</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.3493190705776215</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.3521581888198853</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.3526992201805115</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.3483998775482178</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0.347377210855484</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0.3462404012680054</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0.344974547624588</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.3435662686824799</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.341998428106308</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.3402515947818756</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0.3383060693740845</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.3361369669437408</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0.3337185084819794</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0.3310185074806213</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0.3280013799667358</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0.3246279358863831</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0.2968711853027344</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.3208498358726501</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0.2941471338272095</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0.2919346690177917</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.3166121542453766</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0.2901709675788879</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.2887890934944153</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0.3118468225002289</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0.3064753413200378</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0.4758938550949097</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.3004005551338196</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0.568439781665802</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0.2186561673879623</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0.2934966683387756</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0.188799210804251</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0.09599425882819089</v>
       </c>
     </row>
     <row r="6">
@@ -806,58 +3288,496 @@
         <v>-0.5440883652459572</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3635293245315552</v>
+        <v>-0.8070913553237915</v>
       </c>
       <c r="E6" t="n">
-        <v>0.361009806394577</v>
+        <v>-0.8085529804229736</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3587540090084076</v>
+        <v>-0.8054862022399902</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3663475513458252</v>
+        <v>-0.8098812103271484</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3567353487014771</v>
+        <v>-0.8110854625701904</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3694992363452911</v>
+        <v>-0.8037214279174805</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3730304539203644</v>
+        <v>-0.8121782541275024</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3769847452640533</v>
+        <v>-0.8131670951843262</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3814221918582916</v>
+        <v>-0.8017873764038086</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3864047527313232</v>
+        <v>-0.814064621925354</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4263350069522858</v>
+        <v>-0.8148751258850098</v>
       </c>
       <c r="O6" t="n">
-        <v>0.430095762014389</v>
+        <v>-0.7996723651885986</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4342556893825531</v>
+        <v>-0.815606951713562</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.438854843378067</v>
+        <v>-0.8162691593170166</v>
       </c>
       <c r="R6" t="n">
-        <v>0.443939596414566</v>
+        <v>-0.816868782043457</v>
       </c>
       <c r="S6" t="n">
-        <v>0.449554055929184</v>
+        <v>-0.817409873008728</v>
       </c>
       <c r="T6" t="n">
-        <v>0.339568471113309</v>
+        <v>-0.8178977966308594</v>
       </c>
       <c r="U6" t="n">
-        <v>0.230239183120057</v>
+        <v>-0.7973612546920776</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.8183389902114868</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.8187360763549805</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.8190939426422119</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.8194174766540527</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.8197097778320312</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.7948454618453979</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.7921116352081299</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.8572344779968262</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.8484938144683838</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.840567946434021</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.833385705947876</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.9880993366241455</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.9880977869033813</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.9880990982055664</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.9880993366241455</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.9880980253219604</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.9880996942520142</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.9881008863449097</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.9881000518798828</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.9880989789962769</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.9881011247634888</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.9881000518798828</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.9881011247634888</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.9881007671356201</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.9881001710891724</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.9881006479263306</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.9824749231338501</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.9824776649475098</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.9824841022491455</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0.9824844598770142</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0.9824851751327515</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.9824849367141724</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0.9824849367141724</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0.9824869632720947</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.9824858903884888</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-1.087487578392029</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-1.087099432945251</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-1.087836742401123</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-1.086665511131287</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-1.088149070739746</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-1.088430762290955</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-1.086180806159973</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-1.085640788078308</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-1.085037469863892</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-1.08436381816864</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-1.083613038063049</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-1.082770824432373</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-1.081833720207214</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-1.080785036087036</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-1.079614996910095</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-1.07830822467804</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-1.076848387718201</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-1.075221657752991</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>-1.073407649993896</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-1.080969929695129</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-1.071389317512512</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>-1.077819347381592</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-1.07503342628479</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-1.069147944450378</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-1.072568416595459</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>-1.070380091667175</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-1.06666374206543</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>-1.063918828964233</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-1.844462752342224</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-1.060893535614014</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-1.841284871101379</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0.3186162710189819</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>-1.057579159736633</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0.7754844222430138</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.3316468844229951</v>
       </c>
     </row>
     <row r="7">
@@ -871,58 +3791,496 @@
         <v>3.378684156009972</v>
       </c>
       <c r="D7" t="n">
-        <v>1.923826456069946</v>
+        <v>2.00812292098999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.924792647361755</v>
+        <v>2.004268407821655</v>
       </c>
       <c r="F7" t="n">
-        <v>1.925660252571106</v>
+        <v>2.012404918670654</v>
       </c>
       <c r="G7" t="n">
-        <v>1.922750473022461</v>
+        <v>2.00079607963562</v>
       </c>
       <c r="H7" t="n">
-        <v>1.926442980766296</v>
+        <v>1.997671723365784</v>
       </c>
       <c r="I7" t="n">
-        <v>1.921555399894714</v>
+        <v>2.017158031463623</v>
       </c>
       <c r="J7" t="n">
-        <v>1.920226335525513</v>
+        <v>1.994857549667358</v>
       </c>
       <c r="K7" t="n">
-        <v>1.918745875358582</v>
+        <v>1.992324352264404</v>
       </c>
       <c r="L7" t="n">
-        <v>1.917102217674255</v>
+        <v>2.022435665130615</v>
       </c>
       <c r="M7" t="n">
-        <v>1.91527271270752</v>
+        <v>1.990041255950928</v>
       </c>
       <c r="N7" t="n">
-        <v>1.826247096061707</v>
+        <v>1.987988591194153</v>
       </c>
       <c r="O7" t="n">
-        <v>1.814672708511353</v>
+        <v>2.028294324874878</v>
       </c>
       <c r="P7" t="n">
-        <v>1.801807165145874</v>
+        <v>1.986139893531799</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.787501811981201</v>
+        <v>1.984474897384644</v>
       </c>
       <c r="R7" t="n">
-        <v>1.771600127220154</v>
+        <v>1.982977509498596</v>
       </c>
       <c r="S7" t="n">
-        <v>1.753917813301086</v>
+        <v>1.981627225875854</v>
       </c>
       <c r="T7" t="n">
-        <v>1.961812131128441</v>
+        <v>1.980413913726807</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3707431080437308</v>
+        <v>2.034797191619873</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.979321002960205</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.97833776473999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.977451920509338</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.976654410362244</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.975936651229858</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.042013883590698</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.050022602081299</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.056023359298706</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.061431646347046</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.066298246383667</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.07068133354187</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.978427529335022</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.978427052497864</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.978424787521362</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.978423595428467</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.978422164916992</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.978421568870544</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.978421211242676</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.978419661521912</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.978420495986938</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.978419065475464</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.978418946266174</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.978418111801147</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.978417277336121</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.978416919708252</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.978416085243225</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.120639085769653</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.120635986328125</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.120621919631958</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2.120614290237427</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2.120614767074585</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>2.120612382888794</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2.120613813400269</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>2.120610952377319</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>1.626921534538269</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>1.629289269447327</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.624761700630188</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.631874680519104</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1.622792363166809</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.62099814414978</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>1.634696245193481</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>1.637770056724548</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.641109347343445</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.644728302955627</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.648638010025024</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>1.652849674224854</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>1.657368540763855</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>1.662200331687927</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1.667339682579041</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>1.672781229019165</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1.678507924079895</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>1.684496402740479</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.690711855888367</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>1.795057773590088</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>1.697109937667847</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>1.784648299217224</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.776265978813171</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>1.703634738922119</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>1.769482851028442</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1.76395845413208</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1.710222005844116</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>1.716794013977051</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>1.849801182746887</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>1.723272562026978</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>1.841259598731995</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>1.942587614059448</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>1.72957980632782</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>1.947203709260509</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.1783630057622063</v>
       </c>
     </row>
     <row r="8">
@@ -936,58 +4294,496 @@
         <v>0.3065406805125779</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2073474079370499</v>
+        <v>-0.2054734975099564</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2080225497484207</v>
+        <v>-0.208660677075386</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2086308747529984</v>
+        <v>-0.2019284516572952</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.206598773598671</v>
+        <v>-0.2115284949541092</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2091798335313797</v>
+        <v>-0.2141074687242508</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2057678252458572</v>
+        <v>-0.1979844123125076</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2048480063676834</v>
+        <v>-0.2164259105920792</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.203828290104866</v>
+        <v>-0.2185108810663223</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2027002722024918</v>
+        <v>-0.1935983449220657</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2014497667551041</v>
+        <v>-0.2203881293535233</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2045781165361404</v>
+        <v>-0.2220745831727982</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2053541094064713</v>
+        <v>-0.1887168437242508</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2062047272920609</v>
+        <v>-0.2235934287309647</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2071314007043839</v>
+        <v>-0.2249591499567032</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2081372886896133</v>
+        <v>-0.2261873036623001</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2092278152704239</v>
+        <v>-0.2272936254739761</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1760274339782963</v>
+        <v>-0.2282886654138565</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1243748503715515</v>
+        <v>-0.1832862049341202</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.229184165596962</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.2299901992082596</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.2307135611772537</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.231367900967598</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.2319541722536087</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.177241638302803</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.1705138832330704</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.162692978978157</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.1584645658731461</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.1546424776315689</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.1511883288621902</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.2307218462228775</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.2307223230600357</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.2307223230600357</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.2307234555482864</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.2307228595018387</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.2307232171297073</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.2307227402925491</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.2307223826646805</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.2307222038507462</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.2307222038507462</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.2307219654321671</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0.2307214885950089</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-0.2307226210832596</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.2307224422693253</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.2191780358552933</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0.2191787511110306</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0.2191794067621231</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0.2191779762506485</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-0.2191782742738724</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-0.2191777974367142</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0.219177320599556</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0.2191776782274246</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-0.2191774398088455</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0.2191775590181351</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>-0.219177320599556</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-0.219177320599556</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-0.219177320599556</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.2191774398088455</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-0.1791269928216934</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>-0.1791928559541702</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0.1790666729211807</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>-0.1792604476213455</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0.1790110021829605</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>-0.178958848118782</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-0.179336205124855</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>-0.1794149428606033</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0.1794976145029068</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0.1795835644006729</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>-0.1796714812517166</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0.1797596365213394</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-0.1798474341630936</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0.1799312978982925</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>-0.1800080090761185</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>-0.1800721436738968</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>-0.1801203638315201</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-0.1801425963640213</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>-0.180131807923317</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.001883911667391658</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>-0.1800778657197952</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>-0.01723833195865154</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>-0.03454042598605156</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>-0.1799636632204056</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>-0.05018467828631401</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>-0.06432093679904938</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0.1797763854265213</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-0.1794960051774979</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>-0.1828810721635818</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0.1790954023599625</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>-0.176248624920845</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-1.330962777137756</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>-0.1785473972558975</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>-0.5440086333265461</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.5277928489494415</v>
       </c>
     </row>
     <row r="9">
@@ -1001,58 +4797,496 @@
         <v>0.9261931876026898</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7146961688995361</v>
+        <v>0.7810027599334717</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7160398364067078</v>
+        <v>0.7823671698570251</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7172359824180603</v>
+        <v>0.7794800996780396</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7131880521774292</v>
+        <v>0.7835907936096191</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7183032035827637</v>
+        <v>0.7846879363059998</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7114916443824768</v>
+        <v>0.7777795195579529</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7095814943313599</v>
+        <v>0.7856718897819519</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7074283957481384</v>
+        <v>0.7865553498268127</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7049948573112488</v>
+        <v>0.7758802771568298</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7022430300712585</v>
+        <v>0.7873491644859314</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7228842973709106</v>
+        <v>0.7880597710609436</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7266498208045959</v>
+        <v>0.7737584710121155</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7308458685874939</v>
+        <v>0.7886995077133179</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7355192303657532</v>
+        <v>0.7892745137214661</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7407267093658447</v>
+        <v>0.7897899150848389</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7465286254882812</v>
+        <v>0.7902528047561646</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7320323767596794</v>
+        <v>0.7906689643859863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0515866795750619</v>
+        <v>0.7713851928710938</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7910439372062683</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.7913795113563538</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.7916818261146545</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.7919541597366333</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.7921978831291199</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.7687331438064575</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7657634019851685</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.7643502950668335</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.7622174620628357</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.7602899670600891</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.7585501074790955</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7854517102241516</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.7854524850845337</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.7854518294334412</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.7854518294334412</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.7854520678520203</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.7854519486427307</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.7854524850845337</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.7854536771774292</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.7854526042938232</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.7854527235031128</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.7854540348052979</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.7854540348052979</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.7854540348052979</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.7854537963867188</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.7716779708862305</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.7716791033744812</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.7716814279556274</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.7716845870018005</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.7716837525367737</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.7716843485832214</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.7716843485832214</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.7716854214668274</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.7716858386993408</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.7716859579086304</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.7716858386993408</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.7716858386993408</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.7716858386993408</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.7716853022575378</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.5280373096466064</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.5282527208328247</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.5278407335281372</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.5284878015518188</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.5276633501052856</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.5274999737739563</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.5287448167800903</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.5290263891220093</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.5293328762054443</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.5296652317047119</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.5300267934799194</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.5304181575775146</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.530840277671814</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.5312955975532532</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.5317854881286621</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.5323094725608826</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.5328733921051025</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.5334763526916504</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.5341220498085022</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.4935914874076843</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.5348157286643982</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.497157484292984</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.5007585287094116</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.535567045211792</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.504313051700592</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.5077539682388306</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.5363848805427551</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.5372890830039978</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>1.492284297943115</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.5383093953132629</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>1.488952994346619</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.3430244922637939</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.5394916534423828</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.6086755086549729</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.2184587850528154</v>
       </c>
     </row>
     <row r="10">
@@ -1066,58 +5300,496 @@
         <v>-0.9249289219863195</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3761933445930481</v>
+        <v>0.8040571808815002</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3791617155075073</v>
+        <v>0.8069679737091064</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3818336725234985</v>
+        <v>0.8007886409759521</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3728925585746765</v>
+        <v>0.809562623500824</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3842374682426453</v>
+        <v>0.8118771314620972</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3692246079444885</v>
+        <v>0.7971170544624329</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3651493191719055</v>
+        <v>0.8139438033103943</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3606206178665161</v>
+        <v>0.8157905340194702</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3555880188941956</v>
+        <v>0.7929855585098267</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3499934673309326</v>
+        <v>0.8174397945404053</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3467476367950439</v>
+        <v>0.818916916847229</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3480762839317322</v>
+        <v>0.7883339524269104</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3495513200759888</v>
+        <v>0.8202381134033203</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3511837720870972</v>
+        <v>0.8214224576950073</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.3529891967773438</v>
+        <v>0.822482705116272</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3549870848655701</v>
+        <v>0.8234318494796753</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.39549170630403</v>
+        <v>0.8242853283882141</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1370220776187986</v>
+        <v>0.7830893397331238</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8250501155853271</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.8257348537445068</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8263503909111023</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.8269046545028687</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.8274011611938477</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.7771721482276917</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7704847455024719</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.8411610722541809</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.8281990885734558</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.8164836168289185</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.8059013485908508</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.062047004699707</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.062048316001892</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.062049269676208</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.062050461769104</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.062052488327026</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.062053084373474</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.062052369117737</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.062054872512817</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.062054038047791</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.062054753303528</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.062055349349976</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.062055230140686</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.062055349349976</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.062057495117188</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.062057256698608</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.9514307379722595</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.9514387845993042</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.9514818787574768</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.9515017867088318</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.9515003561973572</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.9515050053596497</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.9515079259872437</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.9515162110328674</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.9515162110328674</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.9515166878700256</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.9515162110328674</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0.7314553260803223</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0.733528733253479</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0.729573130607605</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-0.7358118295669556</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>-0.7278666496276855</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0.7263212203979492</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0.7383224964141846</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0.7410813570022583</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.7441076040267944</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0.7474255561828613</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0.7510539293289185</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0.7550181150436401</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-0.7593393325805664</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-0.7640434503555298</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0.7691476345062256</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0.7746776342391968</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>-0.7806512117385864</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.7870831489562988</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-0.7939924001693726</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-0.8561244010925293</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.8013836145401001</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-0.8562935590744019</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-0.8563723564147949</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-0.80926513671875</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>-0.8563911914825439</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>-0.8563776016235352</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.8176389932632446</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-0.8264955282211304</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-1.603805661201477</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.8358249664306641</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>-1.632229924201965</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.6336405277252197</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>-0.8456053733825684</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.09566506128778791</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.8397643749124922</v>
       </c>
     </row>
     <row r="11">
@@ -1131,58 +5803,496 @@
         <v>0.01239026207722013</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1565708965063095</v>
+        <v>0.1626519411802292</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1613203436136246</v>
+        <v>0.1628895550966263</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1655928641557693</v>
+        <v>0.1623891443014145</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1512929648160934</v>
+        <v>0.1631045788526535</v>
       </c>
       <c r="H11" t="n">
-        <v>0.169440433382988</v>
+        <v>0.1632985919713974</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1454251557588577</v>
+        <v>0.1620974391698837</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1389067322015762</v>
+        <v>0.1634735912084579</v>
       </c>
       <c r="K11" t="n">
-        <v>0.131661668419838</v>
+        <v>0.1636310964822769</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1236086338758469</v>
+        <v>0.1617761701345444</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1146590858697891</v>
+        <v>0.1637736111879349</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1284141391515732</v>
+        <v>0.1639011949300766</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1331148594617844</v>
+        <v>0.1614190191030502</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1383244246244431</v>
+        <v>0.1640176922082901</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1441028565168381</v>
+        <v>0.1641213446855545</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1505068689584732</v>
+        <v>0.1642145365476608</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1576044112443924</v>
+        <v>0.1642996221780777</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1366433294491422</v>
+        <v>0.1643763035535812</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03544687993446714</v>
+        <v>0.1610244959592819</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1644448190927505</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1645068377256393</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1645628958940506</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1646125763654709</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1646585017442703</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1605889350175858</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1601113826036453</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.1528835445642471</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1533208042383194</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.153714582324028</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1540701538324356</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.1567720025777817</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1567705422639847</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1567720025777817</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.1567715257406235</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.1567720025777817</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1567718833684921</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.1567717641592026</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.1567723900079727</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.1567725092172623</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.1567718833684921</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.1567720025777817</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.1567714065313339</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.158303365111351</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.158303365111351</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.1583039611577988</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.1583043187856674</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.1583045870065689</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.158304825425148</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.1583040803670883</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.1583053022623062</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.1583053022623062</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.1583057790994644</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.1583050638437271</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.1583050638437271</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.1583050638437271</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.1583053022623062</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.1723970025777817</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.1726810187101364</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.1721400767564774</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.1729964166879654</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.1719072312116623</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.171696349978447</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.1733429580926895</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.1737263649702072</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.1741488724946976</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.1746149510145187</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.1751264482736588</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.1756899505853653</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.176309272646904</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.176987960934639</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.1777312308549881</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.1785448044538498</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.1794335097074509</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.1803997308015823</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.1814526468515396</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.1915598958730698</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.1825937479734421</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.1915438920259476</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.1915304511785507</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.1838297098875046</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.1915196031332016</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.1915106922388077</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.1851621121168137</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.1865968853235245</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.08692701160907745</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.1881351619958878</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.08568020164966583</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1598697453737259</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.1897798329591751</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.1614183990513496</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.01700353443928477</v>
       </c>
     </row>
     <row r="12">
@@ -1196,58 +6306,496 @@
         <v>1.21134320988949</v>
       </c>
       <c r="D12" t="n">
-        <v>2.513350248336792</v>
+        <v>2.763218402862549</v>
       </c>
       <c r="E12" t="n">
-        <v>2.511744499206543</v>
+        <v>2.764097690582275</v>
       </c>
       <c r="F12" t="n">
-        <v>2.510300397872925</v>
+        <v>2.762229442596436</v>
       </c>
       <c r="G12" t="n">
-        <v>2.515134811401367</v>
+        <v>2.76488208770752</v>
       </c>
       <c r="H12" t="n">
-        <v>2.508999586105347</v>
+        <v>2.765582323074341</v>
       </c>
       <c r="I12" t="n">
-        <v>2.517117261886597</v>
+        <v>2.761117219924927</v>
       </c>
       <c r="J12" t="n">
-        <v>2.519322395324707</v>
+        <v>2.766208648681641</v>
       </c>
       <c r="K12" t="n">
-        <v>2.521772861480713</v>
+        <v>2.766767501831055</v>
       </c>
       <c r="L12" t="n">
-        <v>2.52449893951416</v>
+        <v>2.759865999221802</v>
       </c>
       <c r="M12" t="n">
-        <v>2.527532339096069</v>
+        <v>2.767266511917114</v>
       </c>
       <c r="N12" t="n">
-        <v>2.533147573471069</v>
+        <v>2.767714262008667</v>
       </c>
       <c r="O12" t="n">
-        <v>2.532941818237305</v>
+        <v>2.758455038070679</v>
       </c>
       <c r="P12" t="n">
-        <v>2.532713651657104</v>
+        <v>2.768115997314453</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.532460451126099</v>
+        <v>2.768474817276001</v>
       </c>
       <c r="R12" t="n">
-        <v>2.532180786132812</v>
+        <v>2.768796443939209</v>
       </c>
       <c r="S12" t="n">
-        <v>2.531870603561401</v>
+        <v>2.769085884094238</v>
       </c>
       <c r="T12" t="n">
-        <v>2.445672437311794</v>
+        <v>2.769344329833984</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3182030775821726</v>
+        <v>2.756860494613647</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.769578218460083</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.769786834716797</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.769972324371338</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.770141124725342</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.770291805267334</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.755057573318481</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.753012895584106</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.731230735778809</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.731915235519409</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.732532978057861</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.733092308044434</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.730873346328735</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.730872392654419</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.730873346328735</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.730872392654419</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.730872869491577</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.730872631072998</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.730872631072998</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.730872392654419</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.730872869491577</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.730872869491577</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.730872631072998</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.730872869491577</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2.73087215423584</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.730872392654419</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.734065532684326</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.734066247940063</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.734064817428589</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2.734064102172852</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2.734064340591431</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>2.734063863754272</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>2.904253721237183</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>2.900352716445923</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>2.90776801109314</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>2.896026372909546</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>2.910933971405029</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>2.9137864112854</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>2.89122462272644</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.885900020599365</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>2.879996538162231</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>2.873451232910156</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.866196632385254</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>2.858158588409424</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>2.849256992340088</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2.839399337768555</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.8284912109375</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>2.816423654556274</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>2.803078651428223</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>2.788328886032104</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>2.772034406661987</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.659016609191895</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.75403904914856</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>2.652535676956177</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>2.646621465682983</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.734173536300659</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>2.641263484954834</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>2.636431694030762</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>2.712249994277954</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>2.688059091567993</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>2.566422700881958</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>2.661362171173096</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>2.549700260162354</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>1.69677722454071</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>2.631892919540405</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>2.419497031625228</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.4998675684439483</v>
       </c>
     </row>
     <row r="13">
@@ -1261,58 +6809,496 @@
         <v>0.9113706555551547</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.540099024772644</v>
+        <v>2.639702796936035</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.538912177085876</v>
+        <v>2.63814640045166</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.537842869758606</v>
+        <v>2.641410827636719</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.541418671607971</v>
+        <v>2.636731386184692</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.536880612373352</v>
+        <v>2.63544487953186</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.542880654335022</v>
+        <v>2.643282890319824</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.544503331184387</v>
+        <v>2.634276390075684</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.546303868293762</v>
+        <v>2.633219718933105</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.548293948173523</v>
+        <v>2.645332098007202</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.550493597984314</v>
+        <v>2.632261276245117</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.516523480415344</v>
+        <v>2.631393194198608</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.511162400245667</v>
+        <v>2.647566080093384</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.505193829536438</v>
+        <v>2.630606651306152</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.49854838848114</v>
+        <v>2.629897832870483</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.491148114204407</v>
+        <v>2.629256010055542</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.482904314994812</v>
+        <v>2.628677129745483</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.383631683993654</v>
+        <v>2.628153085708618</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5918072919062356</v>
+        <v>2.649999380111694</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.627681255340576</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.627254962921143</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.626872062683105</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.626522779464722</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.626211643218994</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.652638673782349</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.655495643615723</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.701254367828369</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.698169469833374</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.695387363433838</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.692878723144531</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.744514226913452</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.744512796401978</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.744514226913452</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.744513750076294</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.744514226913452</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.744513034820557</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2.744514226913452</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.744513750076294</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2.744513273239136</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.74451470375061</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.74451470375061</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.744515180587769</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.744516134262085</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.74451732635498</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.72939395904541</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.729392766952515</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.729384660720825</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>2.729381799697876</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>2.729381322860718</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>2.729380369186401</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>2.729379415512085</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>2.729379892349243</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>2.729379653930664</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>2.729379415512085</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>2.729379415512085</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>2.729379415512085</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>2.729379892349243</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0.3837723731994629</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0.382699191570282</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.3847147822380066</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0.3814740777015686</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0.3855430483818054</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>-0.3862718939781189</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0.3800737857818604</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0.3784692883491516</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.3766263127326965</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0.3745090961456299</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0.3720725178718567</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.3692615032196045</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0.3660160303115845</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0.3622614741325378</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0.3579137325286865</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0.3528727293014526</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0.3470229506492615</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.3402256965637207</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0.3323202729225159</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.4686799049377441</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.3231204152107239</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0.4387926459312439</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-0.4127926826477051</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0.3124033808708191</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0.3900693655014038</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0.3701302409172058</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.2999091744422913</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-0.2853250503540039</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>1.98645293712616</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.2682765126228333</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>1.972985625267029</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.1353876441717148</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>-0.2483135014772415</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>1.331815460559894</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>1.381798181966478</v>
       </c>
     </row>
     <row r="14">
@@ -1326,58 +7312,496 @@
         <v>0.07966792776917289</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2851297855377197</v>
+        <v>-0.149164155125618</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2856907248497009</v>
+        <v>-0.1502111107110977</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2861959934234619</v>
+        <v>-0.1480000168085098</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2845065593719482</v>
+        <v>-0.1511526852846146</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2866490483283997</v>
+        <v>-0.1519985347986221</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2838111519813538</v>
+        <v>-0.1467043310403824</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2830361723899841</v>
+        <v>-0.1527598649263382</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2821740508079529</v>
+        <v>-0.1534443646669388</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2812092900276184</v>
+        <v>-0.1452626138925552</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2801309823989868</v>
+        <v>-0.1540589481592178</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3134961128234863</v>
+        <v>-0.1546124368906021</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3184072971343994</v>
+        <v>-0.1436594873666763</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3238683938980103</v>
+        <v>-0.1551106125116348</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.3299354910850525</v>
+        <v>-0.1555576473474503</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.3366830945014954</v>
+        <v>-0.1559612303972244</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3441824316978455</v>
+        <v>-0.1563232690095901</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.277966979558132</v>
+        <v>-0.1566493064165115</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09481223844514187</v>
+        <v>-0.1418756395578384</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.1569414883852005</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1572059541940689</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.157443955540657</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.1576582342386246</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.1578489691019058</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.1398888379335403</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.1376793533563614</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.0853969007730484</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.08965118229389191</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.09343226253986359</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.09679748117923737</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.006407487206161022</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.006407248787581921</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.006409692578017712</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.006410884670913219</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.006411361508071423</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.006410527043044567</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.006410050205886364</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.006412374787032604</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.006411480717360973</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.006412493996322155</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.006412851624190807</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.006413686089217663</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.00641332846134901</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.006415176205337048</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.006414222531020641</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.0752420574426651</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.07524056732654572</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.07523973286151886</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0.07523985207080841</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0.07523985207080841</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-0.07523860037326813</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-0.07523836195468903</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0.07523716986179352</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0.07523716986179352</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0.07523716986179352</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0.07523716986179352</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.07523740828037262</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0.001352262916043401</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0.004087579436600208</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.001130747376009822</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>-0.007098090834915638</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.003383266506716609</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.005424547009170055</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0.01040632743388414</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>-0.0140394689515233</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.01802505366504192</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0.0223893653601408</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0.02715886943042278</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0.032365333288908</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-0.03803683444857597</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-0.04419929906725883</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-0.05087996646761894</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0.05810583755373955</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0.06589354574680328</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.07426066696643829</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>-0.08321864902973175</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>-0.16669000685215</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>-0.09276773035526276</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>-0.1666455417871475</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0.1664783507585526</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0.1029020696878433</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>-0.1662247329950333</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>-0.1659137755632401</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.1136038452386856</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0.124838724732399</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0.6727986335754395</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1365566998720169</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>-0.7364358901977539</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>-0.445841372013092</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0.1486841589212418</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0.1937495822845291</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.1896692369335876</v>
       </c>
     </row>
     <row r="15">
@@ -1391,58 +7815,496 @@
         <v>3.734019556308177</v>
       </c>
       <c r="D15" t="n">
-        <v>3.24721097946167</v>
+        <v>3.011861801147461</v>
       </c>
       <c r="E15" t="n">
-        <v>3.242164611816406</v>
+        <v>3.011255741119385</v>
       </c>
       <c r="F15" t="n">
-        <v>3.237626791000366</v>
+        <v>3.012533903121948</v>
       </c>
       <c r="G15" t="n">
-        <v>3.252821445465088</v>
+        <v>3.010703802108765</v>
       </c>
       <c r="H15" t="n">
-        <v>3.233544826507568</v>
+        <v>3.010205984115601</v>
       </c>
       <c r="I15" t="n">
-        <v>3.259061813354492</v>
+        <v>3.013273239135742</v>
       </c>
       <c r="J15" t="n">
-        <v>3.266002893447876</v>
+        <v>3.009754180908203</v>
       </c>
       <c r="K15" t="n">
-        <v>3.273725509643555</v>
+        <v>3.009345293045044</v>
       </c>
       <c r="L15" t="n">
-        <v>3.282317161560059</v>
+        <v>3.014086961746216</v>
       </c>
       <c r="M15" t="n">
-        <v>3.291876077651978</v>
+        <v>3.008975744247437</v>
       </c>
       <c r="N15" t="n">
-        <v>3.415854215621948</v>
+        <v>3.008642435073853</v>
       </c>
       <c r="O15" t="n">
-        <v>3.429686546325684</v>
+        <v>3.014983415603638</v>
       </c>
       <c r="P15" t="n">
-        <v>3.445053815841675</v>
+        <v>3.008341073989868</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.462125539779663</v>
+        <v>3.008068799972534</v>
       </c>
       <c r="R15" t="n">
-        <v>3.481086015701294</v>
+        <v>3.007823944091797</v>
       </c>
       <c r="S15" t="n">
-        <v>3.502147674560547</v>
+        <v>3.007602214813232</v>
       </c>
       <c r="T15" t="n">
-        <v>3.356254439649885</v>
+        <v>3.007402420043945</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1383750006641859</v>
+        <v>3.015969038009644</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.007222414016724</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.007059097290039</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.006912469863892</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.006780624389648</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.006661415100098</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.01705265045166</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.018241167068481</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.000518798828125</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.003178119659424</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.005598306655884</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.007801294326782</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.963606834411621</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.963605880737305</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.963606834411621</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.963605880737305</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.963606357574463</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.963606119155884</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.963605642318726</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.963603973388672</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.96360445022583</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.963604211807251</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.96360445022583</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.963603496551514</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.963603973388672</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.963605165481567</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.963604927062988</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.981096744537354</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.981101274490356</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.981119394302368</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>2.98112678527832</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>2.981126308441162</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>2.98112964630127</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>2.981131553649902</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>2.98113226890564</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>2.981132984161377</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>2.981132745742798</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>3.367455720901489</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>3.369210004806519</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>3.365865468978882</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>3.371145009994507</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>3.364423990249634</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>3.36312198638916</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>3.373278379440308</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>3.375625610351562</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>3.378204107284546</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>3.381038904190063</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>3.38414740562439</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>3.387552499771118</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>3.391274929046631</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>3.395339965820312</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>3.399769067764282</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>3.404585361480713</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>3.409812688827515</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>3.415471792221069</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>3.421587944030762</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>3.571565866470337</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>3.428182601928711</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>3.564904928207397</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>3.558325290679932</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>3.43528151512146</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>3.551872968673706</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>3.545605182647705</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>3.442909240722656</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>3.451099634170532</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>5.227164268493652</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>3.459887504577637</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>5.344294548034668</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>3.189894914627075</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>3.469322681427002</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>3.162318455165297</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.2954265726089281</v>
       </c>
     </row>
     <row r="16">
@@ -1456,58 +8318,496 @@
         <v>3.776745646201351</v>
       </c>
       <c r="D16" t="n">
-        <v>2.72357964515686</v>
+        <v>2.124613761901855</v>
       </c>
       <c r="E16" t="n">
-        <v>2.724502801895142</v>
+        <v>2.122428417205811</v>
       </c>
       <c r="F16" t="n">
-        <v>2.725330114364624</v>
+        <v>2.127055883407593</v>
       </c>
       <c r="G16" t="n">
-        <v>2.722551584243774</v>
+        <v>2.120474100112915</v>
       </c>
       <c r="H16" t="n">
-        <v>2.726074457168579</v>
+        <v>2.118724584579468</v>
       </c>
       <c r="I16" t="n">
-        <v>2.721403837203979</v>
+        <v>2.129789590835571</v>
       </c>
       <c r="J16" t="n">
-        <v>2.720125675201416</v>
+        <v>2.11715841293335</v>
       </c>
       <c r="K16" t="n">
-        <v>2.718697786331177</v>
+        <v>2.115753412246704</v>
       </c>
       <c r="L16" t="n">
-        <v>2.717102766036987</v>
+        <v>2.132852554321289</v>
       </c>
       <c r="M16" t="n">
-        <v>2.715321063995361</v>
+        <v>2.114494562149048</v>
       </c>
       <c r="N16" t="n">
-        <v>2.696852922439575</v>
+        <v>2.113366365432739</v>
       </c>
       <c r="O16" t="n">
-        <v>2.694922924041748</v>
+        <v>2.136286735534668</v>
       </c>
       <c r="P16" t="n">
-        <v>2.692781209945679</v>
+        <v>2.112353563308716</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.690404653549194</v>
+        <v>2.111444711685181</v>
       </c>
       <c r="R16" t="n">
-        <v>2.687768459320068</v>
+        <v>2.11063027381897</v>
       </c>
       <c r="S16" t="n">
-        <v>2.684844255447388</v>
+        <v>2.109896183013916</v>
       </c>
       <c r="T16" t="n">
-        <v>2.772882929561347</v>
+        <v>2.109237909317017</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2591288481178328</v>
+        <v>2.140139579772949</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.108648300170898</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.108117580413818</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.107639789581299</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.107211589813232</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.10682487487793</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.144466876983643</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.149332523345947</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.258401870727539</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.250174283981323</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.242801189422607</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.236190795898438</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.416176557540894</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.416175842285156</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.416177988052368</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.416177272796631</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.416177749633789</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.41617751121521</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>2.416178464889526</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.416179895401001</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.416179180145264</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.416178941726685</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>2.416179180145264</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.416179418563843</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.416179418563843</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.416180849075317</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.369306802749634</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.369312763214111</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.369337558746338</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2.36935019493103</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.36934757232666</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2.369351387023926</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>2.369353294372559</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>2.369357109069824</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2.369357824325562</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>2.36935830116272</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>2.369357824325562</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>2.369357824325562</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>2.369357824325562</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>2.369357109069824</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>4.132429122924805</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>4.12664270401001</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>4.137667179107666</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>4.120248794555664</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>4.142403125762939</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>4.146682739257812</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>4.113190174102783</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>4.105405330657959</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>4.096822738647461</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>4.087370872497559</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>4.076970100402832</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>4.065537452697754</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>4.052983283996582</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>4.039214611053467</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>4.024135589599609</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>4.007641792297363</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>3.989628553390503</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>3.969992160797119</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>3.948618173599243</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>4.034296989440918</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>3.925400972366333</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>3.97618842124939</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>3.930063486099243</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>3.900232076644897</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>3.89345645904541</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>3.864349603652954</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>3.873008012771606</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>3.84363055229187</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>4.849843502044678</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>3.812013864517212</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>4.901961803436279</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>4.591203212738037</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>3.778088569641113</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>3.357938702663534</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>1.067387747859623</v>
       </c>
     </row>
     <row r="17">
@@ -1521,58 +8821,496 @@
         <v>0.13284922819448</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9980558156967163</v>
+        <v>-0.004089009948074818</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9957238435745239</v>
+        <v>-0.004112971015274525</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9936238527297974</v>
+        <v>-0.004062187857925892</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.000643372535706</v>
+        <v>-0.004130912013351917</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9917305707931519</v>
+        <v>-0.004149866290390491</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.003513693809509</v>
+        <v>-0.00402833241969347</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.006697058677673</v>
+        <v>-0.004165363498032093</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.010228991508484</v>
+        <v>-0.004176569171249866</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.014143705368042</v>
+        <v>-0.003990841098129749</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.018483400344849</v>
+        <v>-0.004188192076981068</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.050236344337463</v>
+        <v>-0.004197848029434681</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.053237795829773</v>
+        <v>-0.003945779986679554</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.056587934494019</v>
+        <v>-0.00420613307505846</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.060327768325806</v>
+        <v>-0.004213822074234486</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.064506053924561</v>
+        <v>-0.004219782538712025</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.069175004959106</v>
+        <v>-0.004224789328873158</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9561215281596882</v>
+        <v>-0.004230928607285023</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2820236864764291</v>
+        <v>-0.003891480388119817</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.004233968444168568</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.004237365908920765</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.00424118060618639</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.004244220443069935</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.004246425814926624</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.0038278226274997</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.003753257216885686</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.006202113814651966</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.005868625827133656</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.005566907115280628</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.005293619818985462</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.005584132857620716</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.005584132857620716</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.005584848113358021</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.005584132857620716</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.005583834834396839</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.005584252066910267</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.005585205741226673</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.005584132857620716</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.005584490485489368</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.00558395404368639</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.005584371276199818</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0.005584490485489368</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.005583834834396839</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-0.005583238787949085</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-0.005583477206528187</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.00209296983666718</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.002093208255246282</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0.002093804301694036</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0.002093446673825383</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-0.002094161929562688</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.002093446673825383</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0.002093446673825383</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.002092492999508977</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.1903881579637527</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.1876626163721085</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.1928432434797287</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.1846307069063187</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.1950489729642868</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.1970361322164536</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0.1812631338834763</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0.1775176376104355</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0.1733522266149521</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0.1687218397855759</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0.1635697931051254</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0.1578354388475418</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0.1514520794153214</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0.1443403512239456</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0.1364165097475052</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0.1275806277990341</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0.117720440030098</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0.1067088693380356</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0.09440042078495026</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>-0.004669916816055775</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0.0806298702955246</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>-0.007042420096695423</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-0.009627652354538441</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0.06519939005374908</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>-0.0123147489503026</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>-0.01502658147364855</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0.04789509251713753</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0.02845500595867634</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>-0.3746821880340576</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0.006585049442946911</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>-0.376405656337738</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0.08451761305332184</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>-0.0180750023573637</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0.03984479441369497</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>0.07541327475633798</v>
       </c>
     </row>
   </sheetData>
